--- a/reference/Profile-History1.5.3.xlsx
+++ b/reference/Profile-History1.5.3.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kohe/GitHub/clinical-core/reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB149946-2676-5147-89DF-B5EBA7ABB12C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C4C49267-F436-644B-853A-674A31460862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51200" yWindow="2520" windowWidth="31700" windowHeight="18000" xr2:uid="{8795F1CA-0AE6-134C-BFF7-10ADAD440A70}"/>
+    <workbookView xWindow="4360" yWindow="500" windowWidth="32000" windowHeight="17500" xr2:uid="{8795F1CA-0AE6-134C-BFF7-10ADAD440A70}"/>
   </bookViews>
   <sheets>
     <sheet name="1.5.3" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -142,19 +143,7 @@
       <t xml:space="preserve">ホｎ </t>
     </rPh>
     <rPh sb="101" eb="103">
-      <t>_x0000__x0008__x0002__x0004_</t>
-    </rPh>
-    <rPh sb="101" eb="103">
-      <t>_x0015__x0002_	1</t>
-    </rPh>
-    <rPh sb="112" eb="114">
-      <t>_x0001__x000D_4_x0001_</t>
-    </rPh>
-    <rPh sb="116" eb="118">
-      <t>_x0010_e_x0002__x0014_e_x0002_</t>
-    </rPh>
-    <rPh sb="118" eb="120">
-      <t/>
+      <t>_x0000__x0008__x0002__x0004__x0015__x0002_	1_x0001__x000D_4_x0001__x0010_e_x0002__x0014_e_x0002_</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -439,13 +428,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -466,9 +455,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -506,7 +495,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -612,7 +601,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -754,7 +743,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
